--- a/Scope_1_stationary_fuel.xlsx
+++ b/Scope_1_stationary_fuel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ebs1-my.sharepoint.com/personal/ritu_stok_com/Documents/Ritu/Python Scripts/Carbon_team_Scripts/Emission_factor_tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{8BD98073-4372-4DD1-A4C0-91BC7D84BA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3E52CAD-B777-46CB-9952-618413A60376}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{8BD98073-4372-4DD1-A4C0-91BC7D84BA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B48E0569-2403-407A-A590-0C35D6AC77F0}"/>
   <bookViews>
-    <workbookView xWindow="10584" yWindow="3996" windowWidth="17280" windowHeight="9960" xr2:uid="{1566BAF8-4A8D-4F98-9E32-C18EFED8963F}"/>
+    <workbookView xWindow="-19812" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{1566BAF8-4A8D-4F98-9E32-C18EFED8963F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="15">
   <si>
     <t>Stationary  combustion fuel</t>
   </si>
@@ -578,131 +578,392 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B6B02DA-DB73-43C1-88F6-75818AD780A4}">
-  <dimension ref="B3:J6"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="26.33203125" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
+    <row r="1" spans="1:9" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>3</v>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4">
+        <v>53.06</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3">
+        <v>2024</v>
+      </c>
+      <c r="H2" s="3">
+        <v>2025</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4">
+        <v>70.22</v>
+      </c>
+      <c r="C3" s="4">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3">
+        <v>2024</v>
+      </c>
+      <c r="H3" s="3">
+        <v>2025</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4">
+        <v>62.87</v>
       </c>
       <c r="C4" s="4">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3">
+        <v>2024</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2025</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4">
         <v>53.06</v>
       </c>
-      <c r="D4" s="4">
+      <c r="C5" s="4">
         <v>1</v>
       </c>
-      <c r="E4" s="4">
+      <c r="D5" s="4">
         <v>0.1</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="3">
+      <c r="E5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="3">
+        <v>2023</v>
+      </c>
+      <c r="H5" s="3">
+        <v>2024</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="4">
+        <v>70.22</v>
+      </c>
+      <c r="C6" s="4">
+        <v>3</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="3">
+        <v>2023</v>
+      </c>
+      <c r="H6" s="3">
+        <v>2024</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4">
+        <v>62.87</v>
+      </c>
+      <c r="C7" s="4">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2023</v>
+      </c>
+      <c r="H7" s="3">
+        <v>2024</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="4">
+        <v>53.06</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="3">
+        <v>2022</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2023</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="4">
+        <v>70.22</v>
+      </c>
+      <c r="C9" s="4">
+        <v>3</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2022</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2023</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="4">
+        <v>62.87</v>
+      </c>
+      <c r="C10" s="4">
+        <v>3</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2022</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2023</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="4">
+        <v>53.06</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="3">
         <v>2021</v>
       </c>
-      <c r="I4" s="3">
+      <c r="H11" s="3">
         <v>2022</v>
       </c>
-      <c r="J4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
+      <c r="I11" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="4">
+      <c r="B12" s="4">
         <v>70.22</v>
       </c>
-      <c r="D5" s="4">
-        <v>3</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="C12" s="4">
+        <v>3</v>
+      </c>
+      <c r="D12" s="4">
         <v>0.6</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="3">
         <v>2021</v>
       </c>
-      <c r="I5" s="3">
+      <c r="H12" s="3">
         <v>2022</v>
       </c>
-      <c r="J5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
+      <c r="I12" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="4">
+      <c r="B13" s="4">
         <v>62.87</v>
       </c>
-      <c r="D6" s="4">
-        <v>3</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="C13" s="4">
+        <v>3</v>
+      </c>
+      <c r="D13" s="4">
         <v>0.6</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="3">
+      <c r="E13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="3">
         <v>2021</v>
       </c>
-      <c r="I6" s="3">
+      <c r="H13" s="3">
         <v>2022</v>
       </c>
-      <c r="J6" t="s">
+      <c r="I13" s="3" t="s">
         <v>14</v>
       </c>
     </row>
